--- a/manual test/Project1 OrangeHRM/OrangeHRM manualtest document.xlsx
+++ b/manual test/Project1 OrangeHRM/OrangeHRM manualtest document.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="12180"/>
+    <workbookView windowWidth="20715" windowHeight="11715" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Requirement" sheetId="1" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="769" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="769" uniqueCount="409">
   <si>
     <t>Reqirement File</t>
   </si>
@@ -200,7 +200,7 @@
     <t>3.1.9</t>
   </si>
   <si>
-    <t xml:space="preserve">ESS user can only see the list of supervisors </t>
+    <t>ESS user can only see the list of supervisors</t>
   </si>
   <si>
     <t>3.1.10</t>
@@ -910,6 +910,9 @@
   </si>
   <si>
     <t>TC_MyInfo_035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESS user can only see the list of supervisors </t>
   </si>
   <si>
     <t>Verify ESS user can see the list of thier own supervisors</t>
@@ -2324,7 +2327,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2373,30 +2376,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -2429,9 +2411,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2742,7 +2721,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="2705735" cy="2133600"/>
+          <a:ext cx="2705735" cy="2228850"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2784,7 +2763,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2581910" y="9525"/>
-          <a:ext cx="4115435" cy="2134235"/>
+          <a:ext cx="4115435" cy="2229485"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2825,8 +2804,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9525" y="2642235"/>
-          <a:ext cx="6858635" cy="3777615"/>
+          <a:off x="9525" y="2832735"/>
+          <a:ext cx="6858635" cy="4730115"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3106,209 +3085,209 @@
     <col min="1" max="1" width="24.8916666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" ht="18" spans="1:14">
       <c r="A1" s="3"/>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33"/>
-      <c r="J1" s="33"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="34"/>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="27"/>
+    </row>
+    <row r="2" ht="18" spans="1:14">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33"/>
-      <c r="I2" s="33"/>
-      <c r="J2" s="33"/>
-      <c r="K2" s="34"/>
-      <c r="L2" s="34"/>
-      <c r="M2" s="34"/>
-      <c r="N2" s="34"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="27"/>
+      <c r="L2" s="27"/>
+      <c r="M2" s="27"/>
+      <c r="N2" s="27"/>
     </row>
     <row r="3" ht="18" spans="1:14">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
-      <c r="E3" s="33"/>
-      <c r="F3" s="33"/>
-      <c r="G3" s="33"/>
-      <c r="H3" s="33"/>
-      <c r="I3" s="33"/>
-      <c r="J3" s="33"/>
-      <c r="K3" s="34"/>
-      <c r="L3" s="34"/>
-      <c r="M3" s="34"/>
-      <c r="N3" s="34"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="26"/>
+      <c r="I3" s="26"/>
+      <c r="J3" s="26"/>
+      <c r="K3" s="27"/>
+      <c r="L3" s="27"/>
+      <c r="M3" s="27"/>
+      <c r="N3" s="27"/>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
-      <c r="E4" s="33"/>
-      <c r="F4" s="33"/>
-      <c r="G4" s="33"/>
-      <c r="H4" s="33"/>
-      <c r="I4" s="33"/>
-      <c r="J4" s="33"/>
-      <c r="K4" s="35" t="s">
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="26"/>
+      <c r="H4" s="26"/>
+      <c r="I4" s="26"/>
+      <c r="J4" s="26"/>
+      <c r="K4" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="L4" s="36"/>
-      <c r="M4" s="36"/>
-      <c r="N4" s="36"/>
-      <c r="O4" s="36"/>
+      <c r="L4" s="28"/>
+      <c r="M4" s="28"/>
+      <c r="N4" s="28"/>
+      <c r="O4" s="28"/>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
-      <c r="E5" s="33"/>
-      <c r="F5" s="33"/>
-      <c r="G5" s="33"/>
-      <c r="H5" s="33"/>
-      <c r="I5" s="33"/>
-      <c r="J5" s="33"/>
-      <c r="K5" s="36"/>
-      <c r="L5" s="36"/>
-      <c r="M5" s="36"/>
-      <c r="N5" s="36"/>
-      <c r="O5" s="36"/>
+      <c r="E5" s="26"/>
+      <c r="F5" s="26"/>
+      <c r="G5" s="26"/>
+      <c r="H5" s="26"/>
+      <c r="I5" s="26"/>
+      <c r="J5" s="26"/>
+      <c r="K5" s="28"/>
+      <c r="L5" s="28"/>
+      <c r="M5" s="28"/>
+      <c r="N5" s="28"/>
+      <c r="O5" s="28"/>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
-      <c r="E6" s="33"/>
-      <c r="F6" s="33"/>
-      <c r="G6" s="33"/>
-      <c r="H6" s="33"/>
-      <c r="I6" s="33"/>
-      <c r="J6" s="33"/>
-      <c r="K6" s="36"/>
-      <c r="L6" s="36"/>
-      <c r="M6" s="36"/>
-      <c r="N6" s="36"/>
-      <c r="O6" s="36"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="26"/>
+      <c r="I6" s="26"/>
+      <c r="J6" s="26"/>
+      <c r="K6" s="28"/>
+      <c r="L6" s="28"/>
+      <c r="M6" s="28"/>
+      <c r="N6" s="28"/>
+      <c r="O6" s="28"/>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
-      <c r="E7" s="33"/>
-      <c r="F7" s="33"/>
-      <c r="G7" s="33"/>
-      <c r="H7" s="33"/>
-      <c r="I7" s="33"/>
-      <c r="J7" s="33"/>
-      <c r="K7" s="36"/>
-      <c r="L7" s="36"/>
-      <c r="M7" s="36"/>
-      <c r="N7" s="36"/>
-      <c r="O7" s="36"/>
+      <c r="E7" s="26"/>
+      <c r="F7" s="26"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="26"/>
+      <c r="I7" s="26"/>
+      <c r="J7" s="26"/>
+      <c r="K7" s="28"/>
+      <c r="L7" s="28"/>
+      <c r="M7" s="28"/>
+      <c r="N7" s="28"/>
+      <c r="O7" s="28"/>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
-      <c r="E8" s="33"/>
-      <c r="F8" s="33"/>
-      <c r="G8" s="33"/>
-      <c r="H8" s="33"/>
-      <c r="I8" s="33"/>
-      <c r="J8" s="33"/>
-      <c r="K8" s="36"/>
-      <c r="L8" s="36"/>
-      <c r="M8" s="36"/>
-      <c r="N8" s="36"/>
-      <c r="O8" s="36"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="26"/>
+      <c r="I8" s="26"/>
+      <c r="J8" s="26"/>
+      <c r="K8" s="28"/>
+      <c r="L8" s="28"/>
+      <c r="M8" s="28"/>
+      <c r="N8" s="28"/>
+      <c r="O8" s="28"/>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
-      <c r="E9" s="33"/>
-      <c r="F9" s="33"/>
-      <c r="G9" s="33"/>
-      <c r="H9" s="33"/>
-      <c r="I9" s="33"/>
-      <c r="J9" s="33"/>
-      <c r="K9" s="36"/>
-      <c r="L9" s="36"/>
-      <c r="M9" s="36"/>
-      <c r="N9" s="36"/>
-      <c r="O9" s="36"/>
+      <c r="E9" s="26"/>
+      <c r="F9" s="26"/>
+      <c r="G9" s="26"/>
+      <c r="H9" s="26"/>
+      <c r="I9" s="26"/>
+      <c r="J9" s="26"/>
+      <c r="K9" s="28"/>
+      <c r="L9" s="28"/>
+      <c r="M9" s="28"/>
+      <c r="N9" s="28"/>
+      <c r="O9" s="28"/>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
-      <c r="E10" s="33"/>
-      <c r="F10" s="33"/>
-      <c r="G10" s="33"/>
-      <c r="H10" s="33"/>
-      <c r="I10" s="33"/>
-      <c r="J10" s="33"/>
-      <c r="K10" s="36"/>
-      <c r="L10" s="36"/>
-      <c r="M10" s="36"/>
-      <c r="N10" s="36"/>
-      <c r="O10" s="36"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="26"/>
+      <c r="I10" s="26"/>
+      <c r="J10" s="26"/>
+      <c r="K10" s="28"/>
+      <c r="L10" s="28"/>
+      <c r="M10" s="28"/>
+      <c r="N10" s="28"/>
+      <c r="O10" s="28"/>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
-      <c r="E11" s="33"/>
-      <c r="F11" s="33"/>
-      <c r="G11" s="33"/>
-      <c r="H11" s="33"/>
-      <c r="I11" s="33"/>
-      <c r="J11" s="33"/>
-      <c r="K11" s="36"/>
-      <c r="L11" s="36"/>
-      <c r="M11" s="36"/>
-      <c r="N11" s="36"/>
-      <c r="O11" s="36"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="26"/>
+      <c r="G11" s="26"/>
+      <c r="H11" s="26"/>
+      <c r="I11" s="26"/>
+      <c r="J11" s="26"/>
+      <c r="K11" s="28"/>
+      <c r="L11" s="28"/>
+      <c r="M11" s="28"/>
+      <c r="N11" s="28"/>
+      <c r="O11" s="28"/>
     </row>
     <row r="12" ht="18" spans="1:14">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
-      <c r="E12" s="33"/>
-      <c r="F12" s="33"/>
-      <c r="G12" s="33"/>
-      <c r="H12" s="33"/>
-      <c r="I12" s="33"/>
-      <c r="J12" s="33"/>
-      <c r="K12" s="34"/>
-      <c r="L12" s="34"/>
-      <c r="M12" s="34"/>
-      <c r="N12" s="34"/>
-    </row>
-    <row r="13" spans="1:14">
+      <c r="E12" s="26"/>
+      <c r="F12" s="26"/>
+      <c r="G12" s="26"/>
+      <c r="H12" s="26"/>
+      <c r="I12" s="26"/>
+      <c r="J12" s="26"/>
+      <c r="K12" s="27"/>
+      <c r="L12" s="27"/>
+      <c r="M12" s="27"/>
+      <c r="N12" s="27"/>
+    </row>
+    <row r="13" ht="18" spans="1:14">
       <c r="A13" s="3" t="s">
         <v>1</v>
       </c>
@@ -3321,12 +3300,12 @@
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
-      <c r="K13" s="34"/>
-      <c r="L13" s="34"/>
-      <c r="M13" s="34"/>
-      <c r="N13" s="34"/>
-    </row>
-    <row r="14" spans="1:14">
+      <c r="K13" s="27"/>
+      <c r="L13" s="27"/>
+      <c r="M13" s="27"/>
+      <c r="N13" s="27"/>
+    </row>
+    <row r="14" ht="18" spans="1:14">
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -3337,136 +3316,136 @@
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
-      <c r="K14" s="34"/>
-      <c r="L14" s="34"/>
-      <c r="M14" s="34"/>
-      <c r="N14" s="34"/>
-    </row>
-    <row r="15" spans="11:14">
-      <c r="K15" s="34"/>
-      <c r="L15" s="34"/>
-      <c r="M15" s="34"/>
-      <c r="N15" s="34"/>
-    </row>
-    <row r="16" spans="11:14">
-      <c r="K16" s="34"/>
-      <c r="L16" s="34"/>
-      <c r="M16" s="34"/>
-      <c r="N16" s="34"/>
-    </row>
-    <row r="17" spans="11:14">
-      <c r="K17" s="34"/>
-      <c r="L17" s="34"/>
-      <c r="M17" s="34"/>
-      <c r="N17" s="34"/>
-    </row>
-    <row r="18" spans="11:14">
-      <c r="K18" s="34"/>
-      <c r="L18" s="34"/>
-      <c r="M18" s="34"/>
-      <c r="N18" s="34"/>
-    </row>
-    <row r="19" spans="11:14">
-      <c r="K19" s="34"/>
-      <c r="L19" s="34"/>
-      <c r="M19" s="34"/>
-      <c r="N19" s="34"/>
-    </row>
-    <row r="20" spans="11:14">
-      <c r="K20" s="34"/>
-      <c r="L20" s="34"/>
-      <c r="M20" s="34"/>
-      <c r="N20" s="34"/>
-    </row>
-    <row r="21" spans="11:14">
-      <c r="K21" s="34"/>
-      <c r="L21" s="34"/>
-      <c r="M21" s="34"/>
-      <c r="N21" s="34"/>
-    </row>
-    <row r="22" spans="11:14">
-      <c r="K22" s="34"/>
-      <c r="L22" s="34"/>
-      <c r="M22" s="34"/>
-      <c r="N22" s="34"/>
-    </row>
-    <row r="23" spans="11:14">
-      <c r="K23" s="34"/>
-      <c r="L23" s="34"/>
-      <c r="M23" s="34"/>
-      <c r="N23" s="34"/>
-    </row>
-    <row r="24" spans="11:14">
-      <c r="K24" s="34"/>
-      <c r="L24" s="34"/>
-      <c r="M24" s="34"/>
-      <c r="N24" s="34"/>
-    </row>
-    <row r="25" spans="11:14">
-      <c r="K25" s="34"/>
-      <c r="L25" s="34"/>
-      <c r="M25" s="34"/>
-      <c r="N25" s="34"/>
-    </row>
-    <row r="26" spans="11:14">
-      <c r="K26" s="34"/>
-      <c r="L26" s="34"/>
-      <c r="M26" s="34"/>
-      <c r="N26" s="34"/>
-    </row>
-    <row r="27" spans="11:14">
-      <c r="K27" s="34"/>
-      <c r="L27" s="34"/>
-      <c r="M27" s="34"/>
-      <c r="N27" s="34"/>
-    </row>
-    <row r="28" spans="11:14">
-      <c r="K28" s="34"/>
-      <c r="L28" s="34"/>
-      <c r="M28" s="34"/>
-      <c r="N28" s="34"/>
-    </row>
-    <row r="29" spans="11:14">
-      <c r="K29" s="34"/>
-      <c r="L29" s="34"/>
-      <c r="M29" s="34"/>
-      <c r="N29" s="34"/>
-    </row>
-    <row r="30" spans="11:14">
-      <c r="K30" s="34"/>
-      <c r="L30" s="34"/>
-      <c r="M30" s="34"/>
-      <c r="N30" s="34"/>
-    </row>
-    <row r="31" spans="11:14">
-      <c r="K31" s="34"/>
-      <c r="L31" s="34"/>
-      <c r="M31" s="34"/>
-      <c r="N31" s="34"/>
-    </row>
-    <row r="32" spans="11:14">
-      <c r="K32" s="34"/>
-      <c r="L32" s="34"/>
-      <c r="M32" s="34"/>
-      <c r="N32" s="34"/>
-    </row>
-    <row r="33" spans="11:14">
-      <c r="K33" s="34"/>
-      <c r="L33" s="34"/>
-      <c r="M33" s="34"/>
-      <c r="N33" s="34"/>
-    </row>
-    <row r="34" spans="11:14">
-      <c r="K34" s="34"/>
-      <c r="L34" s="34"/>
-      <c r="M34" s="34"/>
-      <c r="N34" s="34"/>
-    </row>
-    <row r="35" spans="11:14">
-      <c r="K35" s="34"/>
-      <c r="L35" s="34"/>
-      <c r="M35" s="34"/>
-      <c r="N35" s="34"/>
+      <c r="K14" s="27"/>
+      <c r="L14" s="27"/>
+      <c r="M14" s="27"/>
+      <c r="N14" s="27"/>
+    </row>
+    <row r="15" ht="18" spans="11:14">
+      <c r="K15" s="27"/>
+      <c r="L15" s="27"/>
+      <c r="M15" s="27"/>
+      <c r="N15" s="27"/>
+    </row>
+    <row r="16" ht="18" spans="11:14">
+      <c r="K16" s="27"/>
+      <c r="L16" s="27"/>
+      <c r="M16" s="27"/>
+      <c r="N16" s="27"/>
+    </row>
+    <row r="17" ht="18" spans="11:14">
+      <c r="K17" s="27"/>
+      <c r="L17" s="27"/>
+      <c r="M17" s="27"/>
+      <c r="N17" s="27"/>
+    </row>
+    <row r="18" ht="18" spans="11:14">
+      <c r="K18" s="27"/>
+      <c r="L18" s="27"/>
+      <c r="M18" s="27"/>
+      <c r="N18" s="27"/>
+    </row>
+    <row r="19" ht="18" spans="11:14">
+      <c r="K19" s="27"/>
+      <c r="L19" s="27"/>
+      <c r="M19" s="27"/>
+      <c r="N19" s="27"/>
+    </row>
+    <row r="20" ht="18" spans="11:14">
+      <c r="K20" s="27"/>
+      <c r="L20" s="27"/>
+      <c r="M20" s="27"/>
+      <c r="N20" s="27"/>
+    </row>
+    <row r="21" ht="18" spans="11:14">
+      <c r="K21" s="27"/>
+      <c r="L21" s="27"/>
+      <c r="M21" s="27"/>
+      <c r="N21" s="27"/>
+    </row>
+    <row r="22" ht="18" spans="11:14">
+      <c r="K22" s="27"/>
+      <c r="L22" s="27"/>
+      <c r="M22" s="27"/>
+      <c r="N22" s="27"/>
+    </row>
+    <row r="23" ht="18" spans="11:14">
+      <c r="K23" s="27"/>
+      <c r="L23" s="27"/>
+      <c r="M23" s="27"/>
+      <c r="N23" s="27"/>
+    </row>
+    <row r="24" ht="18" spans="11:14">
+      <c r="K24" s="27"/>
+      <c r="L24" s="27"/>
+      <c r="M24" s="27"/>
+      <c r="N24" s="27"/>
+    </row>
+    <row r="25" ht="18" spans="11:14">
+      <c r="K25" s="27"/>
+      <c r="L25" s="27"/>
+      <c r="M25" s="27"/>
+      <c r="N25" s="27"/>
+    </row>
+    <row r="26" ht="18" spans="11:14">
+      <c r="K26" s="27"/>
+      <c r="L26" s="27"/>
+      <c r="M26" s="27"/>
+      <c r="N26" s="27"/>
+    </row>
+    <row r="27" ht="18" spans="11:14">
+      <c r="K27" s="27"/>
+      <c r="L27" s="27"/>
+      <c r="M27" s="27"/>
+      <c r="N27" s="27"/>
+    </row>
+    <row r="28" ht="18" spans="11:14">
+      <c r="K28" s="27"/>
+      <c r="L28" s="27"/>
+      <c r="M28" s="27"/>
+      <c r="N28" s="27"/>
+    </row>
+    <row r="29" ht="18" spans="11:14">
+      <c r="K29" s="27"/>
+      <c r="L29" s="27"/>
+      <c r="M29" s="27"/>
+      <c r="N29" s="27"/>
+    </row>
+    <row r="30" ht="18" spans="11:14">
+      <c r="K30" s="27"/>
+      <c r="L30" s="27"/>
+      <c r="M30" s="27"/>
+      <c r="N30" s="27"/>
+    </row>
+    <row r="31" ht="18" spans="11:14">
+      <c r="K31" s="27"/>
+      <c r="L31" s="27"/>
+      <c r="M31" s="27"/>
+      <c r="N31" s="27"/>
+    </row>
+    <row r="32" ht="18" spans="11:14">
+      <c r="K32" s="27"/>
+      <c r="L32" s="27"/>
+      <c r="M32" s="27"/>
+      <c r="N32" s="27"/>
+    </row>
+    <row r="33" ht="18" spans="11:14">
+      <c r="K33" s="27"/>
+      <c r="L33" s="27"/>
+      <c r="M33" s="27"/>
+      <c r="N33" s="27"/>
+    </row>
+    <row r="34" ht="18" spans="11:14">
+      <c r="K34" s="27"/>
+      <c r="L34" s="27"/>
+      <c r="M34" s="27"/>
+      <c r="N34" s="27"/>
+    </row>
+    <row r="35" ht="18" spans="11:14">
+      <c r="K35" s="27"/>
+      <c r="L35" s="27"/>
+      <c r="M35" s="27"/>
+      <c r="N35" s="27"/>
     </row>
     <row r="36" spans="1:10">
       <c r="A36" s="3" t="s">
@@ -3557,9 +3536,9 @@
   <dimension ref="A1:D177"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="2" width="9" style="24"/>
-    <col min="3" max="3" width="52.4083333333333" style="25" customWidth="1"/>
-    <col min="4" max="4" width="16.975" style="26" customWidth="1"/>
+    <col min="1" max="2" width="9" style="17"/>
+    <col min="3" max="3" width="52.4083333333333" style="18" customWidth="1"/>
+    <col min="4" max="4" width="16.975" style="19" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -3569,7 +3548,7 @@
       <c r="B1" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="27" t="s">
+      <c r="C1" s="20" t="s">
         <v>14</v>
       </c>
       <c r="D1" s="4" t="s">
@@ -3577,7 +3556,7 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="28">
+      <c r="A2" s="21">
         <v>1</v>
       </c>
       <c r="B2" s="15" t="s">
@@ -3591,7 +3570,7 @@
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="28">
+      <c r="A3" s="21">
         <v>2</v>
       </c>
       <c r="B3" s="15" t="s">
@@ -3605,7 +3584,7 @@
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="28">
+      <c r="A4" s="21">
         <v>3</v>
       </c>
       <c r="B4" s="15" t="s">
@@ -3619,7 +3598,7 @@
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="28">
+      <c r="A5" s="21">
         <v>4</v>
       </c>
       <c r="B5" s="15" t="s">
@@ -3633,7 +3612,7 @@
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="28">
+      <c r="A6" s="21">
         <v>5</v>
       </c>
       <c r="B6" s="15" t="s">
@@ -3647,7 +3626,7 @@
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="28">
+      <c r="A7" s="21">
         <v>6</v>
       </c>
       <c r="B7" s="15" t="s">
@@ -3661,7 +3640,7 @@
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="28">
+      <c r="A8" s="21">
         <v>7</v>
       </c>
       <c r="B8" s="15" t="s">
@@ -3675,7 +3654,7 @@
       </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="28">
+      <c r="A9" s="21">
         <v>8</v>
       </c>
       <c r="B9" s="15" t="s">
@@ -3689,7 +3668,7 @@
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="28">
+      <c r="A10" s="21">
         <v>9</v>
       </c>
       <c r="B10" s="15" t="s">
@@ -3703,7 +3682,7 @@
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="28">
+      <c r="A11" s="21">
         <v>10</v>
       </c>
       <c r="B11" s="15" t="s">
@@ -3717,7 +3696,7 @@
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="28">
+      <c r="A12" s="21">
         <v>11</v>
       </c>
       <c r="B12" s="15" t="s">
@@ -3731,7 +3710,7 @@
       </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="28">
+      <c r="A13" s="21">
         <v>12</v>
       </c>
       <c r="B13" s="15" t="s">
@@ -3745,7 +3724,7 @@
       </c>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="28">
+      <c r="A14" s="21">
         <v>13</v>
       </c>
       <c r="B14" s="15" t="s">
@@ -3759,7 +3738,7 @@
       </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="28">
+      <c r="A15" s="21">
         <v>14</v>
       </c>
       <c r="B15" s="15" t="s">
@@ -3773,7 +3752,7 @@
       </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="28">
+      <c r="A16" s="21">
         <v>15</v>
       </c>
       <c r="B16" s="15" t="s">
@@ -3787,7 +3766,7 @@
       </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="28">
+      <c r="A17" s="21">
         <v>16</v>
       </c>
       <c r="B17" s="15" t="s">
@@ -3796,12 +3775,12 @@
       <c r="C17" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D17" s="29">
+      <c r="D17" s="22">
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="28">
+      <c r="A18" s="21">
         <v>17</v>
       </c>
       <c r="B18" s="15" t="s">
@@ -3815,7 +3794,7 @@
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="28">
+      <c r="A19" s="21">
         <v>18</v>
       </c>
       <c r="B19" s="15" t="s">
@@ -3829,7 +3808,7 @@
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="28">
+      <c r="A20" s="21">
         <v>19</v>
       </c>
       <c r="B20" s="15" t="s">
@@ -3843,7 +3822,7 @@
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="28">
+      <c r="A21" s="21">
         <v>20</v>
       </c>
       <c r="B21" s="15" t="s">
@@ -3857,7 +3836,7 @@
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="28">
+      <c r="A22" s="21">
         <v>21</v>
       </c>
       <c r="B22" s="15" t="s">
@@ -3871,7 +3850,7 @@
       </c>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="28">
+      <c r="A23" s="21">
         <v>22</v>
       </c>
       <c r="B23" s="15" t="s">
@@ -3885,7 +3864,7 @@
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="28">
+      <c r="A24" s="21">
         <v>23</v>
       </c>
       <c r="B24" s="15" t="s">
@@ -3899,7 +3878,7 @@
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="28">
+      <c r="A25" s="21">
         <v>24</v>
       </c>
       <c r="B25" s="15" t="s">
@@ -3913,7 +3892,7 @@
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="28">
+      <c r="A26" s="21">
         <v>25</v>
       </c>
       <c r="B26" s="15" t="s">
@@ -3927,7 +3906,7 @@
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="28">
+      <c r="A27" s="21">
         <v>26</v>
       </c>
       <c r="B27" s="15" t="s">
@@ -3941,7 +3920,7 @@
       </c>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28" s="28">
+      <c r="A28" s="21">
         <v>27</v>
       </c>
       <c r="B28" s="15" t="s">
@@ -3955,7 +3934,7 @@
       </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="28">
+      <c r="A29" s="21">
         <v>28</v>
       </c>
       <c r="B29" s="15" t="s">
@@ -3969,7 +3948,7 @@
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="28">
+      <c r="A30" s="21">
         <v>29</v>
       </c>
       <c r="B30" s="15" t="s">
@@ -3983,7 +3962,7 @@
       </c>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="28">
+      <c r="A31" s="21">
         <v>30</v>
       </c>
       <c r="B31" s="15" t="s">
@@ -3997,7 +3976,7 @@
       </c>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="28">
+      <c r="A32" s="21">
         <v>31</v>
       </c>
       <c r="B32" s="15" t="s">
@@ -4011,7 +3990,7 @@
       </c>
     </row>
     <row r="33" spans="1:4">
-      <c r="A33" s="28">
+      <c r="A33" s="21">
         <v>32</v>
       </c>
       <c r="B33" s="15" t="s">
@@ -4025,7 +4004,7 @@
       </c>
     </row>
     <row r="34" spans="1:4">
-      <c r="A34" s="28">
+      <c r="A34" s="21">
         <v>33</v>
       </c>
       <c r="B34" s="15" t="s">
@@ -4039,7 +4018,7 @@
       </c>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="28">
+      <c r="A35" s="21">
         <v>34</v>
       </c>
       <c r="B35" s="15" t="s">
@@ -4053,7 +4032,7 @@
       </c>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="28">
+      <c r="A36" s="21">
         <v>35</v>
       </c>
       <c r="B36" s="15" t="s">
@@ -4067,7 +4046,7 @@
       </c>
     </row>
     <row r="37" spans="1:4">
-      <c r="A37" s="28">
+      <c r="A37" s="21">
         <v>36</v>
       </c>
       <c r="B37" s="15" t="s">
@@ -4081,7 +4060,7 @@
       </c>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38" s="28">
+      <c r="A38" s="21">
         <v>37</v>
       </c>
       <c r="B38" s="15" t="s">
@@ -4095,7 +4074,7 @@
       </c>
     </row>
     <row r="39" spans="1:4">
-      <c r="A39" s="28">
+      <c r="A39" s="21">
         <v>38</v>
       </c>
       <c r="B39" s="15" t="s">
@@ -4109,7 +4088,7 @@
       </c>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40" s="28">
+      <c r="A40" s="21">
         <v>39</v>
       </c>
       <c r="B40" s="15" t="s">
@@ -4123,7 +4102,7 @@
       </c>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" s="28">
+      <c r="A41" s="21">
         <v>40</v>
       </c>
       <c r="B41" s="15" t="s">
@@ -4137,7 +4116,7 @@
       </c>
     </row>
     <row r="42" spans="1:4">
-      <c r="A42" s="28">
+      <c r="A42" s="21">
         <v>41</v>
       </c>
       <c r="B42" s="15" t="s">
@@ -4151,7 +4130,7 @@
       </c>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" s="28">
+      <c r="A43" s="21">
         <v>42</v>
       </c>
       <c r="B43" s="15" t="s">
@@ -4165,7 +4144,7 @@
       </c>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44" s="28">
+      <c r="A44" s="21">
         <v>43</v>
       </c>
       <c r="B44" s="15" t="s">
@@ -4179,411 +4158,411 @@
       </c>
     </row>
     <row r="45" spans="1:4">
-      <c r="A45" s="28"/>
+      <c r="A45" s="21"/>
       <c r="B45" s="15"/>
-      <c r="C45" s="30" t="s">
+      <c r="C45" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="D45" s="31">
+      <c r="D45" s="24">
         <f>SUM(D2:D44)</f>
         <v>73</v>
       </c>
     </row>
     <row r="46" spans="1:1">
-      <c r="A46" s="32"/>
+      <c r="A46" s="25"/>
     </row>
     <row r="47" spans="1:1">
-      <c r="A47" s="32"/>
+      <c r="A47" s="25"/>
     </row>
     <row r="48" spans="1:1">
-      <c r="A48" s="32"/>
+      <c r="A48" s="25"/>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="32"/>
+      <c r="A49" s="25"/>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="32"/>
+      <c r="A50" s="25"/>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="32"/>
+      <c r="A51" s="25"/>
     </row>
     <row r="52" spans="1:1">
-      <c r="A52" s="32"/>
+      <c r="A52" s="25"/>
     </row>
     <row r="53" spans="1:1">
-      <c r="A53" s="32"/>
+      <c r="A53" s="25"/>
     </row>
     <row r="54" spans="1:1">
-      <c r="A54" s="32"/>
+      <c r="A54" s="25"/>
     </row>
     <row r="55" spans="1:1">
-      <c r="A55" s="32"/>
+      <c r="A55" s="25"/>
     </row>
     <row r="56" spans="1:1">
-      <c r="A56" s="32"/>
+      <c r="A56" s="25"/>
     </row>
     <row r="57" spans="1:1">
-      <c r="A57" s="32"/>
+      <c r="A57" s="25"/>
     </row>
     <row r="58" spans="1:1">
-      <c r="A58" s="32"/>
+      <c r="A58" s="25"/>
     </row>
     <row r="59" spans="1:1">
-      <c r="A59" s="32"/>
+      <c r="A59" s="25"/>
     </row>
     <row r="60" spans="1:1">
-      <c r="A60" s="32"/>
+      <c r="A60" s="25"/>
     </row>
     <row r="61" spans="1:1">
-      <c r="A61" s="32"/>
+      <c r="A61" s="25"/>
     </row>
     <row r="62" spans="1:1">
-      <c r="A62" s="32"/>
+      <c r="A62" s="25"/>
     </row>
     <row r="63" spans="1:1">
-      <c r="A63" s="32"/>
+      <c r="A63" s="25"/>
     </row>
     <row r="64" spans="1:1">
-      <c r="A64" s="32"/>
+      <c r="A64" s="25"/>
     </row>
     <row r="65" spans="1:1">
-      <c r="A65" s="32"/>
+      <c r="A65" s="25"/>
     </row>
     <row r="66" spans="1:1">
-      <c r="A66" s="32"/>
+      <c r="A66" s="25"/>
     </row>
     <row r="67" spans="1:1">
-      <c r="A67" s="32"/>
+      <c r="A67" s="25"/>
     </row>
     <row r="68" spans="1:1">
-      <c r="A68" s="32"/>
+      <c r="A68" s="25"/>
     </row>
     <row r="69" spans="1:1">
-      <c r="A69" s="32"/>
+      <c r="A69" s="25"/>
     </row>
     <row r="70" spans="1:1">
-      <c r="A70" s="32"/>
+      <c r="A70" s="25"/>
     </row>
     <row r="71" spans="1:1">
-      <c r="A71" s="32"/>
+      <c r="A71" s="25"/>
     </row>
     <row r="72" spans="1:1">
-      <c r="A72" s="32"/>
+      <c r="A72" s="25"/>
     </row>
     <row r="73" spans="1:1">
-      <c r="A73" s="32"/>
+      <c r="A73" s="25"/>
     </row>
     <row r="74" spans="1:1">
-      <c r="A74" s="32"/>
+      <c r="A74" s="25"/>
     </row>
     <row r="75" spans="1:1">
-      <c r="A75" s="32"/>
+      <c r="A75" s="25"/>
     </row>
     <row r="76" spans="1:1">
-      <c r="A76" s="32"/>
+      <c r="A76" s="25"/>
     </row>
     <row r="77" spans="1:1">
-      <c r="A77" s="32"/>
+      <c r="A77" s="25"/>
     </row>
     <row r="78" spans="1:1">
-      <c r="A78" s="32"/>
+      <c r="A78" s="25"/>
     </row>
     <row r="79" spans="1:1">
-      <c r="A79" s="32"/>
+      <c r="A79" s="25"/>
     </row>
     <row r="80" spans="1:1">
-      <c r="A80" s="32"/>
+      <c r="A80" s="25"/>
     </row>
     <row r="81" spans="1:1">
-      <c r="A81" s="32"/>
+      <c r="A81" s="25"/>
     </row>
     <row r="82" spans="1:1">
-      <c r="A82" s="32"/>
+      <c r="A82" s="25"/>
     </row>
     <row r="83" spans="1:1">
-      <c r="A83" s="32"/>
+      <c r="A83" s="25"/>
     </row>
     <row r="84" spans="1:1">
-      <c r="A84" s="32"/>
+      <c r="A84" s="25"/>
     </row>
     <row r="85" spans="1:1">
-      <c r="A85" s="32"/>
+      <c r="A85" s="25"/>
     </row>
     <row r="86" spans="1:1">
-      <c r="A86" s="32"/>
+      <c r="A86" s="25"/>
     </row>
     <row r="87" spans="1:1">
-      <c r="A87" s="32"/>
+      <c r="A87" s="25"/>
     </row>
     <row r="88" spans="1:1">
-      <c r="A88" s="32"/>
+      <c r="A88" s="25"/>
     </row>
     <row r="89" spans="1:1">
-      <c r="A89" s="32"/>
+      <c r="A89" s="25"/>
     </row>
     <row r="90" spans="1:1">
-      <c r="A90" s="32"/>
+      <c r="A90" s="25"/>
     </row>
     <row r="91" spans="1:1">
-      <c r="A91" s="32"/>
+      <c r="A91" s="25"/>
     </row>
     <row r="92" spans="1:1">
-      <c r="A92" s="32"/>
+      <c r="A92" s="25"/>
     </row>
     <row r="93" spans="1:1">
-      <c r="A93" s="32"/>
+      <c r="A93" s="25"/>
     </row>
     <row r="94" spans="1:1">
-      <c r="A94" s="32"/>
+      <c r="A94" s="25"/>
     </row>
     <row r="95" spans="1:1">
-      <c r="A95" s="32"/>
+      <c r="A95" s="25"/>
     </row>
     <row r="96" spans="1:1">
-      <c r="A96" s="32"/>
+      <c r="A96" s="25"/>
     </row>
     <row r="97" spans="1:1">
-      <c r="A97" s="32"/>
+      <c r="A97" s="25"/>
     </row>
     <row r="98" spans="1:1">
-      <c r="A98" s="32"/>
+      <c r="A98" s="25"/>
     </row>
     <row r="99" spans="1:1">
-      <c r="A99" s="32"/>
+      <c r="A99" s="25"/>
     </row>
     <row r="100" spans="1:1">
-      <c r="A100" s="32"/>
+      <c r="A100" s="25"/>
     </row>
     <row r="101" spans="1:1">
-      <c r="A101" s="32"/>
+      <c r="A101" s="25"/>
     </row>
     <row r="102" spans="1:1">
-      <c r="A102" s="32"/>
+      <c r="A102" s="25"/>
     </row>
     <row r="103" spans="1:1">
-      <c r="A103" s="32"/>
+      <c r="A103" s="25"/>
     </row>
     <row r="104" spans="1:1">
-      <c r="A104" s="32"/>
+      <c r="A104" s="25"/>
     </row>
     <row r="105" spans="1:1">
-      <c r="A105" s="32"/>
+      <c r="A105" s="25"/>
     </row>
     <row r="106" spans="1:1">
-      <c r="A106" s="32"/>
+      <c r="A106" s="25"/>
     </row>
     <row r="107" spans="1:1">
-      <c r="A107" s="32"/>
+      <c r="A107" s="25"/>
     </row>
     <row r="108" spans="1:1">
-      <c r="A108" s="32"/>
+      <c r="A108" s="25"/>
     </row>
     <row r="109" spans="1:1">
-      <c r="A109" s="32"/>
+      <c r="A109" s="25"/>
     </row>
     <row r="110" spans="1:1">
-      <c r="A110" s="32"/>
+      <c r="A110" s="25"/>
     </row>
     <row r="111" spans="1:1">
-      <c r="A111" s="32"/>
+      <c r="A111" s="25"/>
     </row>
     <row r="112" spans="1:1">
-      <c r="A112" s="32"/>
+      <c r="A112" s="25"/>
     </row>
     <row r="113" spans="1:1">
-      <c r="A113" s="32"/>
+      <c r="A113" s="25"/>
     </row>
     <row r="114" spans="1:1">
-      <c r="A114" s="32"/>
+      <c r="A114" s="25"/>
     </row>
     <row r="115" spans="1:1">
-      <c r="A115" s="32"/>
+      <c r="A115" s="25"/>
     </row>
     <row r="116" spans="1:1">
-      <c r="A116" s="32"/>
+      <c r="A116" s="25"/>
     </row>
     <row r="117" spans="1:1">
-      <c r="A117" s="32"/>
+      <c r="A117" s="25"/>
     </row>
     <row r="118" spans="1:1">
-      <c r="A118" s="32"/>
+      <c r="A118" s="25"/>
     </row>
     <row r="119" spans="1:1">
-      <c r="A119" s="32"/>
+      <c r="A119" s="25"/>
     </row>
     <row r="120" spans="1:1">
-      <c r="A120" s="32"/>
+      <c r="A120" s="25"/>
     </row>
     <row r="121" spans="1:1">
-      <c r="A121" s="32"/>
+      <c r="A121" s="25"/>
     </row>
     <row r="122" spans="1:1">
-      <c r="A122" s="32"/>
+      <c r="A122" s="25"/>
     </row>
     <row r="123" spans="1:1">
-      <c r="A123" s="32"/>
+      <c r="A123" s="25"/>
     </row>
     <row r="124" spans="1:1">
-      <c r="A124" s="32"/>
+      <c r="A124" s="25"/>
     </row>
     <row r="125" spans="1:1">
-      <c r="A125" s="32"/>
+      <c r="A125" s="25"/>
     </row>
     <row r="126" spans="1:1">
-      <c r="A126" s="32"/>
+      <c r="A126" s="25"/>
     </row>
     <row r="127" spans="1:1">
-      <c r="A127" s="32"/>
+      <c r="A127" s="25"/>
     </row>
     <row r="128" spans="1:1">
-      <c r="A128" s="32"/>
+      <c r="A128" s="25"/>
     </row>
     <row r="129" spans="1:1">
-      <c r="A129" s="32"/>
+      <c r="A129" s="25"/>
     </row>
     <row r="130" spans="1:1">
-      <c r="A130" s="32"/>
+      <c r="A130" s="25"/>
     </row>
     <row r="131" spans="1:1">
-      <c r="A131" s="32"/>
+      <c r="A131" s="25"/>
     </row>
     <row r="132" spans="1:1">
-      <c r="A132" s="32"/>
+      <c r="A132" s="25"/>
     </row>
     <row r="133" spans="1:1">
-      <c r="A133" s="32"/>
+      <c r="A133" s="25"/>
     </row>
     <row r="134" spans="1:1">
-      <c r="A134" s="32"/>
+      <c r="A134" s="25"/>
     </row>
     <row r="135" spans="1:1">
-      <c r="A135" s="32"/>
+      <c r="A135" s="25"/>
     </row>
     <row r="136" spans="1:1">
-      <c r="A136" s="32"/>
+      <c r="A136" s="25"/>
     </row>
     <row r="137" spans="1:1">
-      <c r="A137" s="32"/>
+      <c r="A137" s="25"/>
     </row>
     <row r="138" spans="1:1">
-      <c r="A138" s="32"/>
+      <c r="A138" s="25"/>
     </row>
     <row r="139" spans="1:1">
-      <c r="A139" s="32"/>
+      <c r="A139" s="25"/>
     </row>
     <row r="140" spans="1:1">
-      <c r="A140" s="32"/>
+      <c r="A140" s="25"/>
     </row>
     <row r="141" spans="1:1">
-      <c r="A141" s="32"/>
+      <c r="A141" s="25"/>
     </row>
     <row r="142" spans="1:1">
-      <c r="A142" s="32"/>
+      <c r="A142" s="25"/>
     </row>
     <row r="143" spans="1:1">
-      <c r="A143" s="32"/>
+      <c r="A143" s="25"/>
     </row>
     <row r="144" spans="1:1">
-      <c r="A144" s="32"/>
+      <c r="A144" s="25"/>
     </row>
     <row r="145" spans="1:1">
-      <c r="A145" s="32"/>
+      <c r="A145" s="25"/>
     </row>
     <row r="146" spans="1:1">
-      <c r="A146" s="32"/>
+      <c r="A146" s="25"/>
     </row>
     <row r="147" spans="1:1">
-      <c r="A147" s="32"/>
+      <c r="A147" s="25"/>
     </row>
     <row r="148" spans="1:1">
-      <c r="A148" s="32"/>
+      <c r="A148" s="25"/>
     </row>
     <row r="149" spans="1:1">
-      <c r="A149" s="32"/>
+      <c r="A149" s="25"/>
     </row>
     <row r="150" spans="1:1">
-      <c r="A150" s="32"/>
+      <c r="A150" s="25"/>
     </row>
     <row r="151" spans="1:1">
-      <c r="A151" s="32"/>
+      <c r="A151" s="25"/>
     </row>
     <row r="152" spans="1:1">
-      <c r="A152" s="32"/>
+      <c r="A152" s="25"/>
     </row>
     <row r="153" spans="1:1">
-      <c r="A153" s="32"/>
+      <c r="A153" s="25"/>
     </row>
     <row r="154" spans="1:1">
-      <c r="A154" s="32"/>
+      <c r="A154" s="25"/>
     </row>
     <row r="155" spans="1:1">
-      <c r="A155" s="32"/>
+      <c r="A155" s="25"/>
     </row>
     <row r="156" spans="1:1">
-      <c r="A156" s="32"/>
+      <c r="A156" s="25"/>
     </row>
     <row r="157" spans="1:1">
-      <c r="A157" s="32"/>
+      <c r="A157" s="25"/>
     </row>
     <row r="158" spans="1:1">
-      <c r="A158" s="32"/>
+      <c r="A158" s="25"/>
     </row>
     <row r="159" spans="1:1">
-      <c r="A159" s="32"/>
+      <c r="A159" s="25"/>
     </row>
     <row r="160" spans="1:1">
-      <c r="A160" s="32"/>
+      <c r="A160" s="25"/>
     </row>
     <row r="161" spans="1:1">
-      <c r="A161" s="32"/>
+      <c r="A161" s="25"/>
     </row>
     <row r="162" spans="1:1">
-      <c r="A162" s="32"/>
+      <c r="A162" s="25"/>
     </row>
     <row r="163" spans="1:1">
-      <c r="A163" s="32"/>
+      <c r="A163" s="25"/>
     </row>
     <row r="164" spans="1:1">
-      <c r="A164" s="32"/>
+      <c r="A164" s="25"/>
     </row>
     <row r="165" spans="1:1">
-      <c r="A165" s="32"/>
+      <c r="A165" s="25"/>
     </row>
     <row r="166" spans="1:1">
-      <c r="A166" s="32"/>
+      <c r="A166" s="25"/>
     </row>
     <row r="167" spans="1:1">
-      <c r="A167" s="32"/>
+      <c r="A167" s="25"/>
     </row>
     <row r="168" spans="1:1">
-      <c r="A168" s="32"/>
+      <c r="A168" s="25"/>
     </row>
     <row r="169" spans="1:1">
-      <c r="A169" s="32"/>
+      <c r="A169" s="25"/>
     </row>
     <row r="170" spans="1:1">
-      <c r="A170" s="32"/>
+      <c r="A170" s="25"/>
     </row>
     <row r="171" spans="1:1">
-      <c r="A171" s="32"/>
+      <c r="A171" s="25"/>
     </row>
     <row r="172" spans="1:1">
-      <c r="A172" s="32"/>
+      <c r="A172" s="25"/>
     </row>
     <row r="173" spans="1:1">
-      <c r="A173" s="32"/>
+      <c r="A173" s="25"/>
     </row>
     <row r="174" spans="1:1">
-      <c r="A174" s="32"/>
+      <c r="A174" s="25"/>
     </row>
     <row r="175" spans="1:1">
-      <c r="A175" s="32"/>
+      <c r="A175" s="25"/>
     </row>
     <row r="176" spans="1:1">
-      <c r="A176" s="32"/>
+      <c r="A176" s="25"/>
     </row>
     <row r="177" spans="1:1">
-      <c r="A177" s="32"/>
+      <c r="A177" s="25"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5712,29 +5691,29 @@
         <v>44</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>45</v>
+        <v>236</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F36" s="7" t="s">
         <v>84</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H36" s="10" t="s">
         <v>103</v>
       </c>
       <c r="I36" s="8" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="J36" s="5"/>
       <c r="K36" s="5"/>
     </row>
     <row r="37" s="1" customFormat="1" ht="42.75" spans="1:11">
       <c r="A37" s="5" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>82</v>
@@ -5743,29 +5722,29 @@
         <v>44</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>45</v>
+        <v>236</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F37" s="7" t="s">
         <v>84</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H37" s="10" t="s">
         <v>103</v>
       </c>
       <c r="I37" s="8" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="J37" s="5"/>
       <c r="K37" s="5"/>
     </row>
     <row r="38" s="1" customFormat="1" ht="99.75" spans="1:11">
       <c r="A38" s="5" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>82</v>
@@ -5777,26 +5756,26 @@
         <v>47</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F38" s="7" t="s">
         <v>84</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H38" s="11" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="I38" s="8" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="J38" s="5"/>
       <c r="K38" s="5"/>
     </row>
     <row r="39" ht="99.75" spans="1:11">
       <c r="A39" s="5" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B39" s="12" t="s">
         <v>82</v>
@@ -5808,16 +5787,16 @@
         <v>47</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F39" s="7" t="s">
         <v>90</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H39" s="11" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I39" s="8" t="s">
         <v>165</v>
@@ -5827,7 +5806,7 @@
     </row>
     <row r="40" ht="156.75" spans="1:11">
       <c r="A40" s="5" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B40" s="12" t="s">
         <v>82</v>
@@ -5839,26 +5818,26 @@
         <v>48</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F40" s="7" t="s">
         <v>84</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H40" s="11" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="I40" s="8" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="J40" s="15"/>
       <c r="K40" s="15"/>
     </row>
     <row r="41" ht="99.75" spans="1:11">
       <c r="A41" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B41" s="12" t="s">
         <v>82</v>
@@ -5870,26 +5849,26 @@
         <v>49</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F41" s="7" t="s">
         <v>84</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I41" s="8" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="J41" s="15"/>
       <c r="K41" s="15"/>
     </row>
     <row r="42" ht="71.25" spans="1:11">
       <c r="A42" s="5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B42" s="12" t="s">
         <v>82</v>
@@ -5901,26 +5880,26 @@
         <v>49</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F42" s="7" t="s">
         <v>90</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H42" s="10" t="s">
         <v>103</v>
       </c>
       <c r="I42" s="8" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="J42" s="15"/>
       <c r="K42" s="15"/>
     </row>
     <row r="43" ht="114" spans="1:11">
       <c r="A43" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B43" s="12" t="s">
         <v>82</v>
@@ -5929,29 +5908,29 @@
         <v>46</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F43" s="13" t="s">
         <v>84</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H43" s="11" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="I43" s="5" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="J43" s="15"/>
       <c r="K43" s="15"/>
     </row>
     <row r="44" ht="114" spans="1:11">
       <c r="A44" s="5" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B44" s="12" t="s">
         <v>82</v>
@@ -5960,29 +5939,29 @@
         <v>46</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F44" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H44" s="11" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="I44" s="8" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="J44" s="15"/>
       <c r="K44" s="15"/>
     </row>
     <row r="45" ht="199.5" spans="1:11">
       <c r="A45" s="5" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B45" s="12" t="s">
         <v>82</v>
@@ -5991,29 +5970,29 @@
         <v>46</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F45" s="13" t="s">
         <v>84</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H45" s="11" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="I45" s="8" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="J45" s="15"/>
       <c r="K45" s="15"/>
     </row>
     <row r="46" ht="114" spans="1:11">
       <c r="A46" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B46" s="12" t="s">
         <v>82</v>
@@ -6025,26 +6004,26 @@
         <v>52</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F46" s="13" t="s">
         <v>84</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H46" s="11" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="I46" s="5" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="J46" s="15"/>
       <c r="K46" s="15"/>
     </row>
     <row r="47" ht="85.5" spans="1:11">
       <c r="A47" s="5" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B47" s="12" t="s">
         <v>82</v>
@@ -6056,26 +6035,26 @@
         <v>52</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F47" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H47" s="10" t="s">
         <v>103</v>
       </c>
       <c r="I47" s="8" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="J47" s="15"/>
       <c r="K47" s="15"/>
     </row>
     <row r="48" ht="99.75" spans="1:11">
       <c r="A48" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B48" s="12" t="s">
         <v>82</v>
@@ -6087,26 +6066,26 @@
         <v>53</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F48" s="13" t="s">
         <v>84</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H48" s="11" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="I48" s="5" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="J48" s="15"/>
       <c r="K48" s="15"/>
     </row>
     <row r="49" ht="99.75" spans="1:11">
       <c r="A49" s="5" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B49" s="12" t="s">
         <v>82</v>
@@ -6118,26 +6097,26 @@
         <v>53</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F49" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H49" s="10" t="s">
         <v>103</v>
       </c>
       <c r="I49" s="8" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J49" s="15"/>
       <c r="K49" s="15"/>
     </row>
     <row r="50" ht="142.5" spans="1:11">
       <c r="A50" s="5" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B50" s="12" t="s">
         <v>82</v>
@@ -6149,26 +6128,26 @@
         <v>54</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F50" s="13" t="s">
         <v>84</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H50" s="11" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="I50" s="8" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="J50" s="15"/>
       <c r="K50" s="15"/>
     </row>
     <row r="51" ht="99.75" spans="1:11">
       <c r="A51" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B51" s="12" t="s">
         <v>82</v>
@@ -6180,16 +6159,16 @@
         <v>55</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F51" s="13" t="s">
         <v>84</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="I51" s="5" t="s">
         <v>210</v>
@@ -6199,7 +6178,7 @@
     </row>
     <row r="52" ht="71.25" spans="1:11">
       <c r="A52" s="5" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B52" s="12" t="s">
         <v>82</v>
@@ -6211,26 +6190,26 @@
         <v>55</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F52" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H52" s="10" t="s">
         <v>103</v>
       </c>
       <c r="I52" s="8" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="J52" s="15"/>
       <c r="K52" s="15"/>
     </row>
     <row r="53" ht="114" spans="1:11">
       <c r="A53" s="5" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B53" s="12" t="s">
         <v>82</v>
@@ -6242,26 +6221,26 @@
         <v>56</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F53" s="13" t="s">
         <v>84</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H53" s="11" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I53" s="8" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J53" s="15"/>
       <c r="K53" s="15"/>
     </row>
     <row r="54" ht="114" spans="1:11">
       <c r="A54" s="5" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B54" s="12" t="s">
         <v>82</v>
@@ -6273,26 +6252,26 @@
         <v>56</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F54" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G54" s="8" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H54" s="10" t="s">
         <v>103</v>
       </c>
       <c r="I54" s="8" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="J54" s="15"/>
       <c r="K54" s="15"/>
     </row>
     <row r="55" ht="171" spans="1:11">
       <c r="A55" s="5" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B55" s="12" t="s">
         <v>82</v>
@@ -6304,26 +6283,26 @@
         <v>56</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F55" s="13" t="s">
         <v>84</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H55" s="11" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="I55" s="8" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="J55" s="15"/>
       <c r="K55" s="15"/>
     </row>
     <row r="56" ht="114" spans="1:11">
       <c r="A56" s="5" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B56" s="12" t="s">
         <v>82</v>
@@ -6335,26 +6314,26 @@
         <v>58</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F56" s="13" t="s">
         <v>84</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H56" s="10" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="I56" s="5" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="J56" s="15"/>
       <c r="K56" s="15"/>
     </row>
     <row r="57" ht="71.25" spans="1:11">
       <c r="A57" s="5" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B57" s="12" t="s">
         <v>82</v>
@@ -6366,26 +6345,26 @@
         <v>58</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F57" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H57" s="10" t="s">
         <v>103</v>
       </c>
       <c r="I57" s="8" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="J57" s="15"/>
       <c r="K57" s="15"/>
     </row>
     <row r="58" ht="85.5" spans="1:11">
       <c r="A58" s="5" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B58" s="12" t="s">
         <v>82</v>
@@ -6397,26 +6376,26 @@
         <v>59</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F58" s="13" t="s">
         <v>84</v>
       </c>
       <c r="G58" s="8" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H58" s="11" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="I58" s="8" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="J58" s="15"/>
       <c r="K58" s="15"/>
     </row>
     <row r="59" ht="85.5" spans="1:11">
       <c r="A59" s="5" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B59" s="12" t="s">
         <v>82</v>
@@ -6428,26 +6407,26 @@
         <v>59</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F59" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="I59" s="8" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="J59" s="15"/>
       <c r="K59" s="15"/>
     </row>
     <row r="60" ht="128.25" spans="1:11">
       <c r="A60" s="5" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B60" s="12" t="s">
         <v>82</v>
@@ -6459,26 +6438,26 @@
         <v>60</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F60" s="13" t="s">
         <v>84</v>
       </c>
       <c r="G60" s="8" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H60" s="11" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="I60" s="8" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="J60" s="15"/>
       <c r="K60" s="15"/>
     </row>
     <row r="61" ht="99.75" spans="1:11">
       <c r="A61" s="5" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B61" s="12" t="s">
         <v>82</v>
@@ -6490,26 +6469,26 @@
         <v>61</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F61" s="13" t="s">
         <v>84</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="I61" s="8" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="J61" s="15"/>
       <c r="K61" s="15"/>
     </row>
     <row r="62" ht="71.25" spans="1:11">
       <c r="A62" s="5" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B62" s="12" t="s">
         <v>82</v>
@@ -6521,26 +6500,26 @@
         <v>61</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F62" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G62" s="8" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H62" s="10" t="s">
         <v>103</v>
       </c>
       <c r="I62" s="8" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="J62" s="15"/>
       <c r="K62" s="15"/>
     </row>
     <row r="63" ht="114" spans="1:11">
       <c r="A63" s="5" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B63" s="12" t="s">
         <v>82</v>
@@ -6552,26 +6531,26 @@
         <v>62</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F63" s="13" t="s">
         <v>84</v>
       </c>
       <c r="G63" s="8" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H63" s="11" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="I63" s="8" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="J63" s="15"/>
       <c r="K63" s="15"/>
     </row>
     <row r="64" ht="114" spans="1:11">
       <c r="A64" s="5" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B64" s="12" t="s">
         <v>82</v>
@@ -6583,26 +6562,26 @@
         <v>62</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F64" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G64" s="8" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H64" s="11" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="I64" s="8" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="J64" s="15"/>
       <c r="K64" s="15"/>
     </row>
     <row r="65" ht="185.25" spans="1:11">
       <c r="A65" s="5" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B65" s="12" t="s">
         <v>82</v>
@@ -6614,26 +6593,26 @@
         <v>63</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F65" s="13" t="s">
         <v>84</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H65" s="11" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="I65" s="8" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="J65" s="15"/>
       <c r="K65" s="15"/>
     </row>
     <row r="66" ht="99.75" spans="1:11">
       <c r="A66" s="5" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>82</v>
@@ -6645,26 +6624,26 @@
         <v>64</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F66" s="13" t="s">
         <v>84</v>
       </c>
       <c r="G66" s="8" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H66" s="10" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="I66" s="8" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="J66" s="15"/>
       <c r="K66" s="15"/>
     </row>
     <row r="67" ht="71.25" spans="1:11">
       <c r="A67" s="5" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>82</v>
@@ -6676,245 +6655,245 @@
         <v>64</v>
       </c>
       <c r="E67" s="8" t="s">
-        <v>374</v>
-      </c>
-      <c r="F67" s="16" t="s">
+        <v>375</v>
+      </c>
+      <c r="F67" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G67" s="8" t="s">
-        <v>375</v>
-      </c>
-      <c r="H67" s="17" t="s">
+        <v>376</v>
+      </c>
+      <c r="H67" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="I67" s="20" t="s">
-        <v>376</v>
-      </c>
-      <c r="J67" s="23"/>
-      <c r="K67" s="23"/>
+      <c r="I67" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="J67" s="15"/>
+      <c r="K67" s="15"/>
     </row>
     <row r="68" ht="114" spans="1:11">
       <c r="A68" s="5" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="C68" s="18" t="s">
+      <c r="C68" s="6" t="s">
         <v>65</v>
       </c>
       <c r="D68" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="E68" s="19" t="s">
-        <v>378</v>
-      </c>
-      <c r="F68" s="16" t="s">
+      <c r="E68" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="F68" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="G68" s="20" t="s">
-        <v>379</v>
-      </c>
-      <c r="H68" s="21" t="s">
+      <c r="G68" s="8" t="s">
         <v>380</v>
       </c>
-      <c r="I68" s="20" t="s">
+      <c r="H68" s="11" t="s">
         <v>381</v>
       </c>
-      <c r="J68" s="23"/>
-      <c r="K68" s="23"/>
+      <c r="I68" s="8" t="s">
+        <v>382</v>
+      </c>
+      <c r="J68" s="15"/>
+      <c r="K68" s="15"/>
     </row>
     <row r="69" ht="114" spans="1:11">
       <c r="A69" s="5" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="C69" s="18" t="s">
+      <c r="C69" s="6" t="s">
         <v>65</v>
       </c>
       <c r="D69" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="E69" s="19" t="s">
-        <v>383</v>
-      </c>
-      <c r="F69" s="16" t="s">
+      <c r="E69" s="5" t="s">
+        <v>384</v>
+      </c>
+      <c r="F69" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="G69" s="20" t="s">
-        <v>379</v>
-      </c>
-      <c r="H69" s="17" t="s">
+      <c r="G69" s="8" t="s">
+        <v>380</v>
+      </c>
+      <c r="H69" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="I69" s="20" t="s">
-        <v>384</v>
-      </c>
-      <c r="J69" s="23"/>
-      <c r="K69" s="23"/>
+      <c r="I69" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="J69" s="15"/>
+      <c r="K69" s="15"/>
     </row>
     <row r="70" ht="156.75" spans="1:11">
       <c r="A70" s="5" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="C70" s="18" t="s">
+      <c r="C70" s="6" t="s">
         <v>65</v>
       </c>
       <c r="D70" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="E70" s="19" t="s">
-        <v>386</v>
-      </c>
-      <c r="F70" s="16" t="s">
+      <c r="E70" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="F70" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="G70" s="20" t="s">
-        <v>387</v>
-      </c>
-      <c r="H70" s="21" t="s">
+      <c r="G70" s="8" t="s">
         <v>388</v>
       </c>
-      <c r="I70" s="20" t="s">
+      <c r="H70" s="11" t="s">
         <v>389</v>
       </c>
-      <c r="J70" s="23"/>
-      <c r="K70" s="23"/>
+      <c r="I70" s="8" t="s">
+        <v>390</v>
+      </c>
+      <c r="J70" s="15"/>
+      <c r="K70" s="15"/>
     </row>
     <row r="71" ht="114" spans="1:11">
       <c r="A71" s="5" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="C71" s="18" t="s">
+      <c r="C71" s="6" t="s">
         <v>65</v>
       </c>
       <c r="D71" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="E71" s="19" t="s">
-        <v>391</v>
-      </c>
-      <c r="F71" s="16" t="s">
+      <c r="E71" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="F71" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="G71" s="20" t="s">
-        <v>392</v>
-      </c>
-      <c r="H71" s="17" t="s">
+      <c r="G71" s="8" t="s">
         <v>393</v>
       </c>
-      <c r="I71" s="20" t="s">
+      <c r="H71" s="10" t="s">
         <v>394</v>
       </c>
-      <c r="J71" s="23"/>
-      <c r="K71" s="23"/>
+      <c r="I71" s="8" t="s">
+        <v>395</v>
+      </c>
+      <c r="J71" s="15"/>
+      <c r="K71" s="15"/>
     </row>
     <row r="72" ht="85.5" spans="1:11">
       <c r="A72" s="5" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="C72" s="18" t="s">
+      <c r="C72" s="6" t="s">
         <v>65</v>
       </c>
       <c r="D72" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="E72" s="20" t="s">
-        <v>396</v>
-      </c>
-      <c r="F72" s="16" t="s">
+      <c r="E72" s="8" t="s">
+        <v>397</v>
+      </c>
+      <c r="F72" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="G72" s="20" t="s">
-        <v>397</v>
-      </c>
-      <c r="H72" s="17" t="s">
+      <c r="G72" s="8" t="s">
+        <v>398</v>
+      </c>
+      <c r="H72" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="I72" s="20" t="s">
-        <v>398</v>
-      </c>
-      <c r="J72" s="23"/>
-      <c r="K72" s="23"/>
+      <c r="I72" s="8" t="s">
+        <v>399</v>
+      </c>
+      <c r="J72" s="15"/>
+      <c r="K72" s="15"/>
     </row>
     <row r="73" ht="128.25" spans="1:11">
       <c r="A73" s="5" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="C73" s="18" t="s">
+      <c r="C73" s="6" t="s">
         <v>65</v>
       </c>
       <c r="D73" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="E73" s="19" t="s">
-        <v>400</v>
-      </c>
-      <c r="F73" s="16" t="s">
+      <c r="E73" s="5" t="s">
+        <v>401</v>
+      </c>
+      <c r="F73" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="G73" s="20" t="s">
-        <v>401</v>
-      </c>
-      <c r="H73" s="17" t="s">
+      <c r="G73" s="8" t="s">
         <v>402</v>
       </c>
-      <c r="I73" s="20" t="s">
+      <c r="H73" s="10" t="s">
         <v>403</v>
       </c>
-      <c r="J73" s="23"/>
-      <c r="K73" s="23"/>
+      <c r="I73" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="J73" s="15"/>
+      <c r="K73" s="15"/>
     </row>
     <row r="74" ht="128.25" spans="1:11">
       <c r="A74" s="5" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="C74" s="18" t="s">
+      <c r="C74" s="6" t="s">
         <v>65</v>
       </c>
       <c r="D74" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="E74" s="19" t="s">
-        <v>405</v>
-      </c>
-      <c r="F74" s="16" t="s">
+      <c r="E74" s="5" t="s">
+        <v>406</v>
+      </c>
+      <c r="F74" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="G74" s="20" t="s">
-        <v>401</v>
-      </c>
-      <c r="H74" s="21" t="s">
-        <v>406</v>
-      </c>
-      <c r="I74" s="20" t="s">
+      <c r="G74" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="H74" s="11" t="s">
         <v>407</v>
       </c>
-      <c r="J74" s="23"/>
-      <c r="K74" s="23"/>
+      <c r="I74" s="8" t="s">
+        <v>408</v>
+      </c>
+      <c r="J74" s="15"/>
+      <c r="K74" s="15"/>
     </row>
     <row r="75" spans="4:9">
       <c r="D75" s="1"/>
       <c r="E75" s="1"/>
       <c r="G75" s="1"/>
-      <c r="H75" s="22"/>
+      <c r="H75" s="16"/>
       <c r="I75" s="1"/>
     </row>
   </sheetData>
